--- a/Веб-программирование (семестр 6).xlsx
+++ b/Веб-программирование (семестр 6).xlsx
@@ -19,22 +19,33 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
     <t>Номер практики</t>
   </si>
   <si>
     <t>Ссылка</t>
   </si>
+  <si>
+    <t>https://github.com/Tomashevskiy-Artem/Web_semestr_6</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -72,20 +83,23 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Гиперссылка" xfId="1" builtinId="8"/>
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -371,62 +385,64 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="2" t="s">
+      <c r="B1" s="3"/>
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" s="1">
+      <c r="A2" s="3">
         <v>1</v>
       </c>
-      <c r="B2" s="1"/>
-      <c r="C2" s="3"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="4" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="1">
+      <c r="A3" s="3">
         <v>2</v>
       </c>
-      <c r="B3" s="1"/>
-      <c r="C3" s="3"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="2"/>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="1">
+      <c r="A4" s="3">
         <v>3</v>
       </c>
-      <c r="B4" s="1"/>
-      <c r="C4" s="3"/>
+      <c r="B4" s="3"/>
+      <c r="C4" s="2"/>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="1">
+      <c r="A5" s="3">
         <v>4</v>
       </c>
-      <c r="B5" s="1"/>
-      <c r="C5" s="3"/>
+      <c r="B5" s="3"/>
+      <c r="C5" s="2"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" s="1">
+      <c r="A6" s="3">
         <v>5</v>
       </c>
-      <c r="B6" s="1"/>
-      <c r="C6" s="3"/>
+      <c r="B6" s="3"/>
+      <c r="C6" s="2"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" s="1">
+      <c r="A7" s="3">
         <v>6</v>
       </c>
-      <c r="B7" s="1"/>
-      <c r="C7" s="3"/>
+      <c r="B7" s="3"/>
+      <c r="C7" s="2"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" s="1">
+      <c r="A8" s="3">
         <v>7</v>
       </c>
-      <c r="B8" s="1"/>
-      <c r="C8" s="3"/>
+      <c r="B8" s="3"/>
+      <c r="C8" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -439,6 +455,9 @@
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="A6:B6"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="C2" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>